--- a/StructureDefinition-openimis-claim.xlsx
+++ b/StructureDefinition-openimis-claim.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-26T15:39:34+00:00</t>
+    <t>2025-09-08T11:14:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -12427,7 +12427,7 @@
         <v>80</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>22</v>
@@ -13573,7 +13573,7 @@
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>22</v>
@@ -13915,7 +13915,7 @@
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>22</v>
@@ -14031,7 +14031,7 @@
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>22</v>
@@ -14835,7 +14835,7 @@
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>22</v>
@@ -14949,7 +14949,7 @@
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H100" t="s" s="2">
         <v>22</v>
@@ -15065,7 +15065,7 @@
         <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>22</v>
@@ -15753,7 +15753,7 @@
         <v>80</v>
       </c>
       <c r="G107" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H107" t="s" s="2">
         <v>22</v>
@@ -15985,7 +15985,7 @@
         <v>80</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>22</v>
@@ -16889,7 +16889,7 @@
         <v>80</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>22</v>
@@ -18601,7 +18601,7 @@
         <v>80</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>22</v>
@@ -18715,7 +18715,7 @@
         <v>80</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>22</v>
@@ -18943,7 +18943,7 @@
         <v>80</v>
       </c>
       <c r="G135" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H135" t="s" s="2">
         <v>22</v>
@@ -19747,7 +19747,7 @@
         <v>80</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>22</v>
@@ -19861,7 +19861,7 @@
         <v>80</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>22</v>
@@ -20089,7 +20089,7 @@
         <v>80</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>22</v>
@@ -20893,7 +20893,7 @@
         <v>80</v>
       </c>
       <c r="G152" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H152" t="s" s="2">
         <v>22</v>
@@ -21007,7 +21007,7 @@
         <v>80</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>22</v>
@@ -21235,7 +21235,7 @@
         <v>80</v>
       </c>
       <c r="G155" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H155" t="s" s="2">
         <v>22</v>
@@ -22039,7 +22039,7 @@
         <v>80</v>
       </c>
       <c r="G162" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H162" t="s" s="2">
         <v>22</v>
@@ -22153,7 +22153,7 @@
         <v>80</v>
       </c>
       <c r="G163" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>22</v>
@@ -22381,7 +22381,7 @@
         <v>80</v>
       </c>
       <c r="G165" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H165" t="s" s="2">
         <v>22</v>
@@ -23181,7 +23181,7 @@
         <v>80</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H172" t="s" s="2">
         <v>22</v>
@@ -23297,7 +23297,7 @@
         <v>80</v>
       </c>
       <c r="G173" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H173" t="s" s="2">
         <v>22</v>
@@ -23411,7 +23411,7 @@
         <v>80</v>
       </c>
       <c r="G174" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H174" t="s" s="2">
         <v>22</v>
@@ -25127,7 +25127,7 @@
         <v>80</v>
       </c>
       <c r="G189" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H189" t="s" s="2">
         <v>22</v>
@@ -25357,7 +25357,7 @@
         <v>80</v>
       </c>
       <c r="G191" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H191" t="s" s="2">
         <v>22</v>
@@ -25471,7 +25471,7 @@
         <v>80</v>
       </c>
       <c r="G192" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H192" t="s" s="2">
         <v>22</v>
@@ -25587,7 +25587,7 @@
         <v>80</v>
       </c>
       <c r="G193" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H193" t="s" s="2">
         <v>22</v>
@@ -25703,7 +25703,7 @@
         <v>80</v>
       </c>
       <c r="G194" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H194" t="s" s="2">
         <v>22</v>
@@ -27411,7 +27411,7 @@
         <v>80</v>
       </c>
       <c r="G209" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H209" t="s" s="2">
         <v>22</v>
@@ -27525,7 +27525,7 @@
         <v>80</v>
       </c>
       <c r="G210" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H210" t="s" s="2">
         <v>22</v>
@@ -27639,7 +27639,7 @@
         <v>80</v>
       </c>
       <c r="G211" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H211" t="s" s="2">
         <v>22</v>
@@ -27753,7 +27753,7 @@
         <v>80</v>
       </c>
       <c r="G212" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H212" t="s" s="2">
         <v>22</v>
@@ -27867,7 +27867,7 @@
         <v>80</v>
       </c>
       <c r="G213" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H213" t="s" s="2">
         <v>22</v>
@@ -28437,7 +28437,7 @@
         <v>80</v>
       </c>
       <c r="G218" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H218" t="s" s="2">
         <v>22</v>
@@ -28893,7 +28893,7 @@
         <v>80</v>
       </c>
       <c r="G222" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H222" t="s" s="2">
         <v>22</v>
@@ -29009,7 +29009,7 @@
         <v>80</v>
       </c>
       <c r="G223" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H223" t="s" s="2">
         <v>22</v>
@@ -29125,7 +29125,7 @@
         <v>80</v>
       </c>
       <c r="G224" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H224" t="s" s="2">
         <v>22</v>
@@ -29239,7 +29239,7 @@
         <v>80</v>
       </c>
       <c r="G225" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H225" t="s" s="2">
         <v>22</v>
@@ -30039,7 +30039,7 @@
         <v>80</v>
       </c>
       <c r="G232" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H232" t="s" s="2">
         <v>22</v>
@@ -30153,7 +30153,7 @@
         <v>80</v>
       </c>
       <c r="G233" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H233" t="s" s="2">
         <v>22</v>
@@ -30267,7 +30267,7 @@
         <v>80</v>
       </c>
       <c r="G234" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H234" t="s" s="2">
         <v>22</v>
@@ -30953,7 +30953,7 @@
         <v>80</v>
       </c>
       <c r="G240" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H240" t="s" s="2">
         <v>22</v>
@@ -31183,7 +31183,7 @@
         <v>80</v>
       </c>
       <c r="G242" t="s" s="2">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="H242" t="s" s="2">
         <v>22</v>
@@ -31299,7 +31299,7 @@
         <v>80</v>
       </c>
       <c r="G243" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H243" t="s" s="2">
         <v>22</v>
@@ -31413,7 +31413,7 @@
         <v>80</v>
       </c>
       <c r="G244" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H244" t="s" s="2">
         <v>22</v>
@@ -32093,7 +32093,7 @@
         <v>80</v>
       </c>
       <c r="G250" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H250" t="s" s="2">
         <v>22</v>
@@ -32209,7 +32209,7 @@
         <v>80</v>
       </c>
       <c r="G251" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H251" t="s" s="2">
         <v>22</v>

--- a/StructureDefinition-openimis-claim.xlsx
+++ b/StructureDefinition-openimis-claim.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:14:40+00:00</t>
+    <t>2025-09-08T11:37:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-openimis-claim.xlsx
+++ b/StructureDefinition-openimis-claim.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-08T11:37:47+00:00</t>
+    <t>2025-09-08T11:49:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
